--- a/streamlit_deploy/truyvan_thuyvan/Lưu lượng Sản lượng Srepok3 1977_2026.xlsx
+++ b/streamlit_deploy/truyvan_thuyvan/Lưu lượng Sản lượng Srepok3 1977_2026.xlsx
@@ -5904,7 +5904,7 @@
         <v>128.93</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>66.8944957</v>
+        <v>107.8024148</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
@@ -5937,7 +5937,7 @@
         <v>344.33</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>406.88</v>
+        <v>401.25</v>
       </c>
     </row>
     <row r="53" spans="2:28" ht="15" ns3:dyDescent="0.25">
